--- a/Working_File1.xlsx
+++ b/Working_File1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\offic\Desktop\School\Virtual Enviornment and Py\Zag2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A236F74-5224-4D15-BEDC-95D248FB3D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF14442E-2237-461A-866D-D370B8674303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-13905" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-13905" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10158,4 +10159,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A2AD991-1958-4DF5-9AF0-A3379B59A263}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>